--- a/data/sample/sitrang/Sitrang_ddm.xlsx
+++ b/data/sample/sitrang/Sitrang_ddm.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim\Desktop\FIBF\Data\ddm\DDM ground survey data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim\IBF-Analysis\data\sample\sitrang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602876E1-F405-441D-8EAE-C3518832C10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37665BB5-8C3D-46F2-966B-9E847D785270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="House" sheetId="5" r:id="rId1"/>
     <sheet name="Agriculture" sheetId="6" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Agriculture!$A$2:$H$159</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="191">
   <si>
     <t xml:space="preserve">Bagerhat  </t>
   </si>
@@ -47,18 +50,12 @@
     <t xml:space="preserve">Barguna  </t>
   </si>
   <si>
-    <t xml:space="preserve">Barishal  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Bhola  </t>
   </si>
   <si>
     <t xml:space="preserve">Chandpur  </t>
   </si>
   <si>
-    <t xml:space="preserve">Chattogram  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Cox's Bazar  </t>
   </si>
   <si>
@@ -131,12 +128,6 @@
     <t xml:space="preserve">Patharghata  </t>
   </si>
   <si>
-    <t xml:space="preserve">Taltali  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agailjhara  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Babuganj  </t>
   </si>
   <si>
@@ -479,9 +470,6 @@
     <t xml:space="preserve">Brahmanbaria  </t>
   </si>
   <si>
-    <t xml:space="preserve">Cumilla  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Dhaka  </t>
   </si>
   <si>
@@ -500,24 +488,12 @@
     <t xml:space="preserve">Shariatpur  </t>
   </si>
   <si>
-    <t>Mohanagar</t>
-  </si>
-  <si>
     <t>Karnaphuli</t>
   </si>
   <si>
     <t>Indurkani</t>
   </si>
   <si>
-    <t>Dhaka North City</t>
-  </si>
-  <si>
-    <t>Dhaka South City</t>
-  </si>
-  <si>
-    <t>Adorrso Sadar</t>
-  </si>
-  <si>
     <t>Fully Damaged Agricultural Land</t>
   </si>
   <si>
@@ -621,6 +597,24 @@
   </si>
   <si>
     <t>Total_loss_amount_land</t>
+  </si>
+  <si>
+    <t>Taltoli</t>
+  </si>
+  <si>
+    <t>Agailjhara</t>
+  </si>
+  <si>
+    <t>Barisal</t>
+  </si>
+  <si>
+    <t>Chittagong</t>
+  </si>
+  <si>
+    <t>Comilla</t>
+  </si>
+  <si>
+    <t>Comilla Adarsha Sadar</t>
   </si>
 </sst>
 </file>
@@ -696,14 +690,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B76AAC1-050C-4C97-8EA3-E399D533C78E}">
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -996,49 +990,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
+      <c r="C1" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1046,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1080,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1092,7 +1086,7 @@
         <v>118</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F67" si="0">C4+D4+E4</f>
+        <f t="shared" ref="F4:F66" si="0">C4+D4+E4</f>
         <v>134</v>
       </c>
       <c r="G4">
@@ -1105,7 +1099,7 @@
         <v>1320000</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J67" si="1">G4+H4+I4</f>
+        <f t="shared" ref="J4:J66" si="1">G4+H4+I4</f>
         <v>2120000</v>
       </c>
     </row>
@@ -1114,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1148,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1182,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1216,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1250,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1284,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1318,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1352,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1386,7 +1380,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1420,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1454,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1488,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1522,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1553,10 +1547,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1587,10 +1581,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1621,10 +1615,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1655,10 +1649,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1689,10 +1683,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1723,10 +1717,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -1757,10 +1751,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1791,10 +1785,10 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1825,10 +1819,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1859,10 +1853,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1893,10 +1887,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1927,10 +1921,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1961,10 +1955,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1995,10 +1989,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2029,10 +2023,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2063,10 +2057,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -2097,10 +2091,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2131,10 +2125,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2165,10 +2159,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2199,10 +2193,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2233,10 +2227,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2267,10 +2261,10 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2301,10 +2295,10 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -2335,10 +2329,10 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2369,10 +2363,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2403,10 +2397,10 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2437,10 +2431,10 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2471,10 +2465,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2505,10 +2499,10 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2539,10 +2533,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2573,10 +2567,10 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2607,10 +2601,10 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2641,10 +2635,10 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2675,10 +2669,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2709,10 +2703,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2743,10 +2737,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2777,10 +2771,10 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2811,10 +2805,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2845,10 +2839,10 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2879,10 +2873,10 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2913,10 +2907,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2925,11 +2919,11 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2938,19 +2932,19 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>1000000</v>
+        <v>514500</v>
       </c>
       <c r="J58">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>514500</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2959,11 +2953,11 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2972,19 +2966,19 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>514500</v>
+        <v>262500</v>
       </c>
       <c r="J59">
         <f t="shared" si="1"/>
-        <v>514500</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2993,11 +2987,11 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="F60">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -3006,19 +3000,19 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>262500</v>
+        <v>861000</v>
       </c>
       <c r="J60">
         <f t="shared" si="1"/>
-        <v>262500</v>
+        <v>861000</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3027,11 +3021,11 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="F61">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -3040,19 +3034,19 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>861000</v>
+        <v>493500</v>
       </c>
       <c r="J61">
         <f t="shared" si="1"/>
-        <v>861000</v>
+        <v>493500</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -3061,11 +3055,11 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>25</v>
+        <v>566</v>
       </c>
       <c r="F62">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>566</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3074,19 +3068,19 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>493500</v>
+        <v>6667500</v>
       </c>
       <c r="J62">
         <f t="shared" si="1"/>
-        <v>493500</v>
+        <v>6667500</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3095,11 +3089,11 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>566</v>
+        <v>896</v>
       </c>
       <c r="F63">
         <f t="shared" si="0"/>
-        <v>566</v>
+        <v>896</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -3108,19 +3102,19 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>6667500</v>
+        <v>10258500</v>
       </c>
       <c r="J63">
         <f t="shared" si="1"/>
-        <v>6667500</v>
+        <v>10258500</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -3129,11 +3123,11 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>896</v>
+        <v>196</v>
       </c>
       <c r="F64">
         <f t="shared" si="0"/>
-        <v>896</v>
+        <v>196</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3142,19 +3136,19 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>10258500</v>
+        <v>2058000</v>
       </c>
       <c r="J64">
         <f t="shared" si="1"/>
-        <v>10258500</v>
+        <v>2058000</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3163,11 +3157,11 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="F65">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3176,19 +3170,19 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>2058000</v>
+        <v>1081500</v>
       </c>
       <c r="J65">
         <f t="shared" si="1"/>
-        <v>2058000</v>
+        <v>1081500</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3197,11 +3191,11 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="F66">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3210,19 +3204,19 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>1081500</v>
+        <v>0</v>
       </c>
       <c r="J66">
         <f t="shared" si="1"/>
-        <v>1081500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3234,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="F67">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F67:F130" si="2">C67+D67+E67</f>
         <v>0</v>
       </c>
       <c r="G67">
@@ -3247,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J67:J130" si="3">G67+H67+I67</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3268,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="F68">
-        <f t="shared" ref="F68:F131" si="2">C68+D68+E68</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G68">
@@ -3281,16 +3275,16 @@
         <v>0</v>
       </c>
       <c r="J68">
-        <f t="shared" ref="J68:J131" si="3">G68+H68+I68</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3321,10 +3315,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3333,11 +3327,11 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F70">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3346,19 +3340,19 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>227000</v>
       </c>
       <c r="J70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>227000</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3367,11 +3361,11 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="F71">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3380,19 +3374,19 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>227000</v>
+        <v>1950000</v>
       </c>
       <c r="J71">
         <f t="shared" si="3"/>
-        <v>227000</v>
+        <v>1950000</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3401,11 +3395,11 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="F72">
         <f t="shared" si="2"/>
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3414,19 +3408,19 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>1950000</v>
+        <v>9240000</v>
       </c>
       <c r="J72">
         <f t="shared" si="3"/>
-        <v>1950000</v>
+        <v>9240000</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B73" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3435,11 +3429,11 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F73">
         <f t="shared" si="2"/>
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3448,19 +3442,19 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>9240000</v>
+        <v>4380000</v>
       </c>
       <c r="J73">
         <f t="shared" si="3"/>
-        <v>9240000</v>
+        <v>4380000</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -3469,11 +3463,11 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F74">
         <f t="shared" si="2"/>
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3482,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>4380000</v>
+        <v>6870000</v>
       </c>
       <c r="J74">
         <f t="shared" si="3"/>
-        <v>4380000</v>
+        <v>6870000</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3503,11 +3497,11 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <f t="shared" si="2"/>
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3516,19 +3510,19 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>6870000</v>
+        <v>0</v>
       </c>
       <c r="J75">
         <f t="shared" si="3"/>
-        <v>6870000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3537,11 +3531,11 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F76">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3550,19 +3544,19 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>5850000</v>
       </c>
       <c r="J76">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5850000</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3571,11 +3565,11 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F77">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3584,19 +3578,19 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>5850000</v>
+        <v>0</v>
       </c>
       <c r="J77">
         <f t="shared" si="3"/>
-        <v>5850000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3627,180 +3621,180 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="F79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>15120000</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>40760000</v>
       </c>
       <c r="J79">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>55880000</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="E80">
-        <v>286</v>
+        <v>218</v>
       </c>
       <c r="F80">
         <f t="shared" si="2"/>
-        <v>412</v>
+        <v>251</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>15120000</v>
+        <v>1650000</v>
       </c>
       <c r="I80">
-        <v>40760000</v>
+        <v>34280000</v>
       </c>
       <c r="J80">
         <f t="shared" si="3"/>
-        <v>55880000</v>
+        <v>35930000</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>33</v>
+        <v>370</v>
       </c>
       <c r="E81">
-        <v>218</v>
+        <v>460</v>
       </c>
       <c r="F81">
         <f t="shared" si="2"/>
-        <v>251</v>
+        <v>830</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>1650000</v>
+        <v>96200000</v>
       </c>
       <c r="I81">
-        <v>34280000</v>
+        <v>12180402</v>
       </c>
       <c r="J81">
         <f t="shared" si="3"/>
-        <v>35930000</v>
+        <v>108380402</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
         <v>8</v>
       </c>
-      <c r="B82" t="s">
-        <v>107</v>
-      </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <v>370</v>
-      </c>
       <c r="E82">
-        <v>460</v>
+        <v>47</v>
       </c>
       <c r="F82">
         <f t="shared" si="2"/>
-        <v>830</v>
+        <v>55</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82">
-        <v>96200000</v>
+        <v>200000</v>
       </c>
       <c r="I82">
-        <v>12180402</v>
+        <v>470000</v>
       </c>
       <c r="J82">
         <f t="shared" si="3"/>
-        <v>108380402</v>
+        <v>670000</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>47</v>
+        <v>922</v>
       </c>
       <c r="F83">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>922</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>470000</v>
+        <v>28500000</v>
       </c>
       <c r="J83">
         <f t="shared" si="3"/>
-        <v>670000</v>
+        <v>28500000</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3809,11 +3803,11 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>922</v>
+        <v>100</v>
       </c>
       <c r="F84">
         <f t="shared" si="2"/>
-        <v>922</v>
+        <v>100</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -3822,16 +3816,16 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>28500000</v>
+        <v>5000000</v>
       </c>
       <c r="J84">
         <f t="shared" si="3"/>
-        <v>28500000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
         <v>108</v>
@@ -3843,11 +3837,11 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F85">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3856,19 +3850,19 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>5000000</v>
+        <v>18800000</v>
       </c>
       <c r="J85">
         <f t="shared" si="3"/>
-        <v>5000000</v>
+        <v>18800000</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3877,11 +3871,11 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="F86">
         <f t="shared" si="2"/>
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -3890,19 +3884,19 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>18800000</v>
+        <v>8280000</v>
       </c>
       <c r="J86">
         <f t="shared" si="3"/>
-        <v>18800000</v>
+        <v>8280000</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3911,11 +3905,11 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="F87">
         <f t="shared" si="2"/>
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3924,16 +3918,16 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>8280000</v>
+        <v>13500000</v>
       </c>
       <c r="J87">
         <f t="shared" si="3"/>
-        <v>8280000</v>
+        <v>13500000</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
@@ -3945,11 +3939,11 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F88">
         <f t="shared" si="2"/>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -3958,19 +3952,19 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>13500000</v>
+        <v>0</v>
       </c>
       <c r="J88">
         <f t="shared" si="3"/>
-        <v>13500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -4001,10 +3995,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4013,11 +4007,11 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F90">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -4026,19 +4020,19 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>690000</v>
       </c>
       <c r="J90">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4047,11 +4041,11 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="F91">
         <f t="shared" si="2"/>
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -4060,87 +4054,87 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>690000</v>
+        <v>100000</v>
       </c>
       <c r="J91">
         <f t="shared" si="3"/>
-        <v>690000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B92" t="s">
         <v>113</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="F92">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>2100000</v>
       </c>
       <c r="I92">
-        <v>100000</v>
+        <v>10500000</v>
       </c>
       <c r="J92">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>13230000</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C93">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F93">
         <f t="shared" si="2"/>
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="G93">
-        <v>630000</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>10500000</v>
+        <v>9300000</v>
       </c>
       <c r="J93">
         <f t="shared" si="3"/>
-        <v>13230000</v>
+        <v>9300000</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -4149,11 +4143,11 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <f t="shared" si="2"/>
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -4162,87 +4156,87 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>9300000</v>
+        <v>0</v>
       </c>
       <c r="J94">
         <f t="shared" si="3"/>
-        <v>9300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>9777</v>
       </c>
       <c r="F95">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>9827</v>
       </c>
       <c r="G95">
         <v>0</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>537600000</v>
       </c>
       <c r="J95">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>540100000</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E96">
-        <v>9777</v>
+        <v>1050</v>
       </c>
       <c r="F96">
         <f t="shared" si="2"/>
-        <v>9827</v>
+        <v>1050</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>537600000</v>
+        <v>94500000</v>
       </c>
       <c r="J96">
         <f t="shared" si="3"/>
-        <v>540100000</v>
+        <v>94500000</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4251,11 +4245,11 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="F97">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -4264,19 +4258,19 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>94500000</v>
+        <v>9000000</v>
       </c>
       <c r="J97">
         <f t="shared" si="3"/>
-        <v>94500000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B98" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4285,11 +4279,11 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="F98">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -4298,19 +4292,19 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>9000000</v>
+        <v>11400000</v>
       </c>
       <c r="J98">
         <f t="shared" si="3"/>
-        <v>9000000</v>
+        <v>11400000</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B99" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4319,11 +4313,11 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="F99">
         <f t="shared" si="2"/>
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -4332,19 +4326,19 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>11400000</v>
+        <v>15000000</v>
       </c>
       <c r="J99">
         <f t="shared" si="3"/>
-        <v>11400000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -4353,11 +4347,11 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="F100">
         <f t="shared" si="2"/>
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -4366,19 +4360,19 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>15000000</v>
+        <v>53000000</v>
       </c>
       <c r="J100">
         <f t="shared" si="3"/>
-        <v>15000000</v>
+        <v>53000000</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4387,11 +4381,11 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="F101">
         <f t="shared" si="2"/>
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -4400,155 +4394,155 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>53000000</v>
+        <v>22125000</v>
       </c>
       <c r="J101">
         <f t="shared" si="3"/>
-        <v>53000000</v>
+        <v>22125000</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E102">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="F102">
         <f t="shared" si="2"/>
-        <v>220</v>
+        <v>470</v>
       </c>
       <c r="G102">
         <v>0</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>25000000</v>
       </c>
       <c r="I102">
-        <v>22125000</v>
+        <v>13500000</v>
       </c>
       <c r="J102">
         <f t="shared" si="3"/>
-        <v>22125000</v>
+        <v>38500000</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="E103">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="F103">
         <f t="shared" si="2"/>
-        <v>470</v>
+        <v>305</v>
       </c>
       <c r="G103">
         <v>0</v>
       </c>
       <c r="H103">
-        <v>25000000</v>
+        <v>240000</v>
       </c>
       <c r="I103">
-        <v>13500000</v>
+        <v>11790000</v>
       </c>
       <c r="J103">
         <f t="shared" si="3"/>
-        <v>38500000</v>
+        <v>12030000</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E104">
-        <v>293</v>
+        <v>230</v>
       </c>
       <c r="F104">
         <f t="shared" si="2"/>
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G104">
         <v>0</v>
       </c>
       <c r="H104">
-        <v>240000</v>
+        <v>3500000</v>
       </c>
       <c r="I104">
-        <v>11790000</v>
+        <v>11500000</v>
       </c>
       <c r="J104">
         <f t="shared" si="3"/>
-        <v>12030000</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="F105">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G105">
         <v>0</v>
       </c>
       <c r="H105">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="I105">
-        <v>11500000</v>
+        <v>750000</v>
       </c>
       <c r="J105">
         <f t="shared" si="3"/>
-        <v>15000000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4557,11 +4551,11 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F106">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -4570,19 +4564,19 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>750000</v>
+        <v>445000</v>
       </c>
       <c r="J106">
         <f t="shared" si="3"/>
-        <v>750000</v>
+        <v>445000</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -4591,11 +4585,11 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F107">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -4604,19 +4598,19 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>445000</v>
+        <v>105000</v>
       </c>
       <c r="J107">
         <f t="shared" si="3"/>
-        <v>445000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4625,11 +4619,11 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F108">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -4638,19 +4632,19 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>105000</v>
+        <v>805000</v>
       </c>
       <c r="J108">
         <f t="shared" si="3"/>
-        <v>105000</v>
+        <v>805000</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4659,11 +4653,11 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>39</v>
+        <v>213</v>
       </c>
       <c r="F109">
         <f t="shared" si="2"/>
-        <v>39</v>
+        <v>213</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -4672,87 +4666,87 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>805000</v>
+        <v>3195000</v>
       </c>
       <c r="J109">
         <f t="shared" si="3"/>
-        <v>805000</v>
+        <v>3195000</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="E110">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <f t="shared" si="2"/>
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="G110">
         <v>0</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>4700000</v>
       </c>
       <c r="I110">
-        <v>3195000</v>
+        <v>0</v>
       </c>
       <c r="J110">
         <f t="shared" si="3"/>
-        <v>3195000</v>
+        <v>4700000</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F111">
         <f t="shared" si="2"/>
-        <v>235</v>
+        <v>10</v>
       </c>
       <c r="G111">
         <v>0</v>
       </c>
       <c r="H111">
-        <v>4700000</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="J111">
         <f t="shared" si="3"/>
-        <v>4700000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -4761,11 +4755,11 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F112">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -4774,87 +4768,87 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>150000</v>
+        <v>1090000</v>
       </c>
       <c r="J112">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>1090000</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="E113">
-        <v>50</v>
+        <v>1606</v>
       </c>
       <c r="F113">
         <f t="shared" si="2"/>
-        <v>50</v>
+        <v>1728</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>9049950</v>
       </c>
       <c r="I113">
-        <v>1090000</v>
+        <v>44263668</v>
       </c>
       <c r="J113">
         <f t="shared" si="3"/>
-        <v>1090000</v>
+        <v>53563618</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>1606</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <f t="shared" si="2"/>
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>9049950</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>44263668</v>
+        <v>0</v>
       </c>
       <c r="J114">
         <f t="shared" si="3"/>
-        <v>53563618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -4885,10 +4879,10 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4919,10 +4913,10 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -4953,10 +4947,10 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -4987,10 +4981,10 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5021,10 +5015,10 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -5033,11 +5027,11 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F120">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -5046,155 +5040,155 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>23000000</v>
       </c>
       <c r="J120">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23000000</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B121" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="E121">
-        <v>160</v>
+        <v>1533</v>
       </c>
       <c r="F121">
         <f t="shared" si="2"/>
-        <v>160</v>
+        <v>1756</v>
       </c>
       <c r="G121">
         <v>0</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>53000000</v>
       </c>
       <c r="I121">
-        <v>23000000</v>
+        <v>181290000</v>
       </c>
       <c r="J121">
         <f t="shared" si="3"/>
-        <v>23000000</v>
+        <v>234290000</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B122" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>1533</v>
+        <v>288</v>
       </c>
       <c r="F122">
         <f t="shared" si="2"/>
-        <v>1756</v>
+        <v>288</v>
       </c>
       <c r="G122">
         <v>0</v>
       </c>
       <c r="H122">
-        <v>53000000</v>
+        <v>0</v>
       </c>
       <c r="I122">
-        <v>181290000</v>
+        <v>36470000</v>
       </c>
       <c r="J122">
         <f t="shared" si="3"/>
-        <v>234290000</v>
+        <v>36470000</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B123" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E123">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="F123">
         <f t="shared" si="2"/>
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="G123">
         <v>0</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>13000000</v>
       </c>
       <c r="I123">
-        <v>36470000</v>
+        <v>26900000</v>
       </c>
       <c r="J123">
         <f t="shared" si="3"/>
-        <v>36470000</v>
+        <v>39900000</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B124" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>230</v>
+        <v>129</v>
       </c>
       <c r="F124">
         <f t="shared" si="2"/>
-        <v>280</v>
+        <v>129</v>
       </c>
       <c r="G124">
         <v>0</v>
       </c>
       <c r="H124">
-        <v>13000000</v>
+        <v>0</v>
       </c>
       <c r="I124">
-        <v>26900000</v>
+        <v>13890000</v>
       </c>
       <c r="J124">
         <f t="shared" si="3"/>
-        <v>39900000</v>
+        <v>13890000</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B125" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -5203,11 +5197,11 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="F125">
         <f t="shared" si="2"/>
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -5216,87 +5210,87 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>13890000</v>
+        <v>2240000</v>
       </c>
       <c r="J125">
         <f t="shared" si="3"/>
-        <v>13890000</v>
+        <v>2240000</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E126">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="F126">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>328</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="I126">
-        <v>2240000</v>
+        <v>3295000</v>
       </c>
       <c r="J126">
         <f t="shared" si="3"/>
-        <v>2240000</v>
+        <v>5195000</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C127">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="F127">
         <f t="shared" si="2"/>
-        <v>328</v>
+        <v>1</v>
       </c>
       <c r="G127">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="I127">
-        <v>3295000</v>
+        <v>100000</v>
       </c>
       <c r="J127">
         <f t="shared" si="3"/>
-        <v>5195000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -5305,11 +5299,11 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -5318,19 +5312,19 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J128">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B129" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -5361,10 +5355,10 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -5395,10 +5389,10 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B131" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5407,11 +5401,11 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F131">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" ref="F131:F158" si="4">C131+D131+E131</f>
+        <v>28</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -5420,19 +5414,19 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="J131">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" ref="J131:J158" si="5">G131+H131+I131</f>
+        <v>1500000</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B132" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5441,11 +5435,11 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F132">
-        <f t="shared" ref="F132:F161" si="4">C132+D132+E132</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>43</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -5454,53 +5448,53 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>0</v>
+        <v>2150000</v>
       </c>
       <c r="J132">
-        <f t="shared" ref="J132:J161" si="5">G132+H132+I132</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2150000</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B133" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E133">
         <v>0</v>
       </c>
       <c r="F133">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G133">
         <v>0</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="I133">
         <v>0</v>
       </c>
       <c r="J133">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -5509,11 +5503,11 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F134">
         <f t="shared" si="4"/>
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -5522,19 +5516,19 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>1500000</v>
+        <v>250000</v>
       </c>
       <c r="J134">
         <f t="shared" si="5"/>
-        <v>1500000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -5543,11 +5537,11 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -5556,53 +5550,53 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>2150000</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <f t="shared" si="5"/>
-        <v>2150000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B136" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F136">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="G136">
         <v>0</v>
       </c>
       <c r="H136">
-        <v>650000</v>
+        <v>0</v>
       </c>
       <c r="I136">
-        <v>0</v>
+        <v>4450000</v>
       </c>
       <c r="J136">
         <f t="shared" si="5"/>
-        <v>650000</v>
+        <v>4450000</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -5611,11 +5605,11 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F137">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -5624,53 +5618,53 @@
         <v>0</v>
       </c>
       <c r="I137">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="J137">
         <f t="shared" si="5"/>
-        <v>250000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G138">
         <v>0</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>61000000</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="J138">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>62500000</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -5679,11 +5673,11 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="F139">
         <f t="shared" si="4"/>
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="G139">
         <v>0</v>
@@ -5692,19 +5686,19 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>4450000</v>
+        <v>14800000</v>
       </c>
       <c r="J139">
         <f t="shared" si="5"/>
-        <v>4450000</v>
+        <v>14800000</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B140" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5713,11 +5707,11 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F140">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="G140">
         <v>0</v>
@@ -5726,87 +5720,87 @@
         <v>0</v>
       </c>
       <c r="I140">
-        <v>500000</v>
+        <v>4300000</v>
       </c>
       <c r="J140">
         <f t="shared" si="5"/>
-        <v>500000</v>
+        <v>4300000</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E141">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F141">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G141">
         <v>0</v>
       </c>
       <c r="H141">
-        <v>61000000</v>
+        <v>2000000</v>
       </c>
       <c r="I141">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="J141">
         <f t="shared" si="5"/>
-        <v>62500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E142">
-        <v>232</v>
+        <v>58</v>
       </c>
       <c r="F142">
         <f t="shared" si="4"/>
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="I142">
-        <v>14800000</v>
+        <v>1450000</v>
       </c>
       <c r="J142">
         <f t="shared" si="5"/>
-        <v>14800000</v>
+        <v>5450000</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B143" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5815,11 +5809,11 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="F143">
         <f t="shared" si="4"/>
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -5828,155 +5822,155 @@
         <v>0</v>
       </c>
       <c r="I143">
-        <v>4300000</v>
+        <v>750000</v>
       </c>
       <c r="J143">
         <f t="shared" si="5"/>
-        <v>4300000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B144" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F144">
         <f t="shared" si="4"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G144">
         <v>0</v>
       </c>
       <c r="H144">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="I144">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="J144">
         <f t="shared" si="5"/>
-        <v>3000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B145" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F145">
         <f t="shared" si="4"/>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="I145">
-        <v>1450000</v>
+        <v>0</v>
       </c>
       <c r="J145">
         <f t="shared" si="5"/>
-        <v>5450000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F146">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>182</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>7600000</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
       <c r="I146">
-        <v>750000</v>
+        <v>6000000</v>
       </c>
       <c r="J146">
         <f t="shared" si="5"/>
-        <v>750000</v>
+        <v>13600000</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G147">
         <v>0</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="I147">
         <v>0</v>
       </c>
       <c r="J147">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -5985,11 +5979,11 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -5998,87 +5992,87 @@
         <v>0</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="J148">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="C149">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F149">
         <f t="shared" si="4"/>
-        <v>182</v>
+        <v>5</v>
       </c>
       <c r="G149">
-        <v>7600000</v>
+        <v>0</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>6000000</v>
+        <v>500000</v>
       </c>
       <c r="J149">
         <f t="shared" si="5"/>
-        <v>13600000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B150" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G150">
         <v>0</v>
       </c>
       <c r="H150">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>0</v>
       </c>
       <c r="J150">
         <f t="shared" si="5"/>
-        <v>2400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B151" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6087,11 +6081,11 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151">
         <v>0</v>
@@ -6100,19 +6094,19 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J151">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B152" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6121,11 +6115,11 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F152">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -6134,19 +6128,19 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>500000</v>
+        <v>2730000</v>
       </c>
       <c r="J152">
         <f t="shared" si="5"/>
-        <v>500000</v>
+        <v>2730000</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B153" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -6155,11 +6149,11 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F153">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -6168,19 +6162,19 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="J153">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>950000</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B154" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6189,11 +6183,11 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F154">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -6202,19 +6196,19 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>1400000</v>
       </c>
       <c r="J154">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B155" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6223,11 +6217,11 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -6236,19 +6230,19 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>2730000</v>
+        <v>0</v>
       </c>
       <c r="J155">
         <f t="shared" si="5"/>
-        <v>2730000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6257,11 +6251,11 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F156">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -6270,19 +6264,19 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>950000</v>
+        <v>0</v>
       </c>
       <c r="J156">
         <f t="shared" si="5"/>
-        <v>950000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B157" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -6291,11 +6285,11 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F157">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -6304,19 +6298,19 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>1400000</v>
+        <v>0</v>
       </c>
       <c r="J157">
         <f t="shared" si="5"/>
-        <v>1400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B158" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -6341,108 +6335,6 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>145</v>
-      </c>
-      <c r="B159" t="s">
-        <v>171</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="E159">
-        <v>0</v>
-      </c>
-      <c r="F159">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G159">
-        <v>0</v>
-      </c>
-      <c r="H159">
-        <v>0</v>
-      </c>
-      <c r="I159">
-        <v>0</v>
-      </c>
-      <c r="J159">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>145</v>
-      </c>
-      <c r="B160" t="s">
-        <v>170</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160">
-        <v>0</v>
-      </c>
-      <c r="F160">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-      <c r="H160">
-        <v>0</v>
-      </c>
-      <c r="I160">
-        <v>0</v>
-      </c>
-      <c r="J160">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>145</v>
-      </c>
-      <c r="B161" t="s">
-        <v>48</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="E161">
-        <v>0</v>
-      </c>
-      <c r="F161">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G161">
-        <v>0</v>
-      </c>
-      <c r="H161">
-        <v>0</v>
-      </c>
-      <c r="I161">
-        <v>0</v>
-      </c>
-      <c r="J161">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -6458,7 +6350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B736AE-F99C-45C4-9672-CAAAC6EF5EAE}">
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -6470,43 +6362,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="H1" s="5"/>
+      <c r="C1" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>193</v>
+        <v>153</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -6514,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -6542,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
@@ -6557,11 +6449,11 @@
         <v>9870390</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G67" si="0">C4+E4</f>
+        <f t="shared" ref="G4:G66" si="0">C4+E4</f>
         <v>418</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H67" si="1">D4+F4</f>
+        <f t="shared" ref="H4:H66" si="1">D4+F4</f>
         <v>10070390</v>
       </c>
     </row>
@@ -6570,7 +6462,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>12</v>
@@ -6598,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -6626,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>16</v>
@@ -6654,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
@@ -6682,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1">
         <v>38</v>
@@ -6710,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>0.5</v>
@@ -6738,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>0.5</v>
@@ -6766,7 +6658,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1">
         <v>2</v>
@@ -6794,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
@@ -6822,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
@@ -6850,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
@@ -6878,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1">
         <v>1.5</v>
@@ -6906,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1">
         <v>1.5</v>
@@ -6931,10 +6823,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="C18" s="1">
         <v>1.36</v>
@@ -6959,10 +6851,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -6987,10 +6879,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -7015,10 +6907,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C21" s="1">
         <v>5.69</v>
@@ -7043,10 +6935,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1">
         <v>10.78</v>
@@ -7071,10 +6963,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1">
         <v>0</v>
@@ -7099,10 +6991,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -7127,10 +7019,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1">
         <v>10</v>
@@ -7155,10 +7047,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C26" s="1">
         <v>0</v>
@@ -7183,10 +7075,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1">
         <v>0</v>
@@ -7211,10 +7103,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C28" s="1">
         <v>282</v>
@@ -7239,10 +7131,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C29" s="1">
         <v>331</v>
@@ -7267,10 +7159,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1">
         <v>0</v>
@@ -7295,10 +7187,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31" s="1">
         <v>0</v>
@@ -7323,10 +7215,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C32" s="1">
         <v>0</v>
@@ -7351,10 +7243,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C33" s="1">
         <v>50</v>
@@ -7379,10 +7271,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
@@ -7407,10 +7299,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C35" s="1">
         <v>0</v>
@@ -7435,10 +7327,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C36" s="1">
         <v>0</v>
@@ -7463,10 +7355,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C37" s="1">
         <v>7.5</v>
@@ -7491,10 +7383,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C38" s="1">
         <v>16</v>
@@ -7519,10 +7411,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1">
         <v>0</v>
@@ -7547,10 +7439,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
@@ -7575,10 +7467,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1">
         <v>0</v>
@@ -7603,10 +7495,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C42" s="1">
         <v>0</v>
@@ -7631,10 +7523,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C43" s="1">
         <v>0</v>
@@ -7659,10 +7551,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
@@ -7687,10 +7579,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C45" s="1">
         <v>0</v>
@@ -7715,10 +7607,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C46" s="1">
         <v>165</v>
@@ -7743,10 +7635,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C47" s="1">
         <v>0</v>
@@ -7771,10 +7663,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C48" s="1">
         <v>0</v>
@@ -7799,10 +7691,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C49" s="1">
         <v>0</v>
@@ -7827,10 +7719,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C50" s="1">
         <v>0</v>
@@ -7855,10 +7747,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C51" s="1">
         <v>29</v>
@@ -7883,10 +7775,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C52" s="1">
         <v>3</v>
@@ -7911,10 +7803,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C53" s="1">
         <v>100</v>
@@ -7939,10 +7831,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C54" s="1">
         <v>0</v>
@@ -7967,10 +7859,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C55" s="1">
         <v>0</v>
@@ -7995,10 +7887,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C56" s="1">
         <v>0</v>
@@ -8023,10 +7915,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C57" s="1">
         <v>0</v>
@@ -8051,10 +7943,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -8063,26 +7955,26 @@
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>0</v>
+        <v>74.23</v>
       </c>
       <c r="F58" s="1">
-        <v>0</v>
+        <v>1410370</v>
       </c>
       <c r="G58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>74.23</v>
       </c>
       <c r="H58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1410370</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59" s="1">
         <v>0</v>
@@ -8091,26 +7983,26 @@
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>74.23</v>
+        <v>22.25</v>
       </c>
       <c r="F59" s="1">
-        <v>1410370</v>
+        <v>422750</v>
       </c>
       <c r="G59">
         <f t="shared" si="0"/>
-        <v>74.23</v>
+        <v>22.25</v>
       </c>
       <c r="H59">
         <f t="shared" si="1"/>
-        <v>1410370</v>
+        <v>422750</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C60" s="1">
         <v>0</v>
@@ -8119,26 +8011,26 @@
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="F60" s="1">
-        <v>422750</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <f t="shared" si="0"/>
-        <v>22.25</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <f t="shared" si="1"/>
-        <v>422750</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C61" s="1">
         <v>0</v>
@@ -8147,26 +8039,26 @@
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>138320</v>
       </c>
       <c r="G61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="H61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>138320</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C62" s="1">
         <v>0</v>
@@ -8175,26 +8067,26 @@
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>7.28</v>
+        <v>132.24</v>
       </c>
       <c r="F62" s="1">
-        <v>138320</v>
+        <v>2512560</v>
       </c>
       <c r="G62">
         <f t="shared" si="0"/>
-        <v>7.28</v>
+        <v>132.24</v>
       </c>
       <c r="H62">
         <f t="shared" si="1"/>
-        <v>138320</v>
+        <v>2512560</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C63" s="1">
         <v>0</v>
@@ -8203,26 +8095,26 @@
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>132.24</v>
+        <v>70.73</v>
       </c>
       <c r="F63" s="1">
-        <v>2512560</v>
+        <v>1343870</v>
       </c>
       <c r="G63">
         <f t="shared" si="0"/>
-        <v>132.24</v>
+        <v>70.73</v>
       </c>
       <c r="H63">
         <f t="shared" si="1"/>
-        <v>2512560</v>
+        <v>1343870</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="C64" s="1">
         <v>0</v>
@@ -8231,26 +8123,26 @@
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>70.73</v>
+        <v>20.53</v>
       </c>
       <c r="F64" s="1">
-        <v>1343870</v>
+        <v>390070</v>
       </c>
       <c r="G64">
         <f t="shared" si="0"/>
-        <v>70.73</v>
+        <v>20.53</v>
       </c>
       <c r="H64">
         <f t="shared" si="1"/>
-        <v>1343870</v>
+        <v>390070</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="C65" s="1">
         <v>0</v>
@@ -8259,26 +8151,26 @@
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>20.53</v>
+        <v>45.46</v>
       </c>
       <c r="F65" s="1">
-        <v>390070</v>
+        <v>863740</v>
       </c>
       <c r="G65">
         <f t="shared" si="0"/>
-        <v>20.53</v>
+        <v>45.46</v>
       </c>
       <c r="H65">
         <f t="shared" si="1"/>
-        <v>390070</v>
+        <v>863740</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C66" s="1">
         <v>0</v>
@@ -8287,26 +8179,26 @@
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>45.46</v>
+        <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>863740</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <f t="shared" si="0"/>
-        <v>45.46</v>
+        <v>0</v>
       </c>
       <c r="H66">
         <f t="shared" si="1"/>
-        <v>863740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C67" s="1">
         <v>0</v>
@@ -8321,20 +8213,20 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G67:G130" si="2">C67+E67</f>
         <v>0</v>
       </c>
       <c r="H67">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H67:H130" si="3">D67+F67</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C68" s="1">
         <v>0</v>
@@ -8349,20 +8241,20 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G131" si="2">C68+E68</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H68">
-        <f t="shared" ref="H68:H131" si="3">D68+F68</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C69" s="1">
         <v>0</v>
@@ -8387,10 +8279,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C70" s="1">
         <v>0</v>
@@ -8399,26 +8291,26 @@
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G70">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" s="1">
         <v>0</v>
@@ -8427,250 +8319,250 @@
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F71" s="1">
-        <v>500000</v>
+        <v>1901250</v>
       </c>
       <c r="G71">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="H71">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>1901250</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="C72" s="1">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>6840900</v>
       </c>
       <c r="E72" s="1">
-        <v>65</v>
+        <v>3488</v>
       </c>
       <c r="F72" s="1">
-        <v>1901250</v>
+        <v>6439999.04</v>
       </c>
       <c r="G72">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>4478</v>
       </c>
       <c r="H72">
         <f t="shared" si="3"/>
-        <v>1901250</v>
+        <v>13280899.039999999</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B73" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C73" s="1">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="D73" s="1">
-        <v>6840900</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>3488</v>
+        <v>750</v>
       </c>
       <c r="F73" s="1">
-        <v>6439999.04</v>
+        <v>7500000</v>
       </c>
       <c r="G73">
         <f t="shared" si="2"/>
-        <v>4478</v>
+        <v>750</v>
       </c>
       <c r="H73">
         <f t="shared" si="3"/>
-        <v>13280899.039999999</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C74" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>2375440</v>
       </c>
       <c r="E74" s="1">
-        <v>750</v>
+        <v>256.5</v>
       </c>
       <c r="F74" s="1">
-        <v>7500000</v>
+        <v>4495162.5</v>
       </c>
       <c r="G74">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>348.5</v>
       </c>
       <c r="H74">
         <f t="shared" si="3"/>
-        <v>7500000</v>
+        <v>6870602.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C75" s="1">
-        <v>92</v>
+        <v>310</v>
       </c>
       <c r="D75" s="1">
-        <v>2375440</v>
+        <v>8004200</v>
       </c>
       <c r="E75" s="1">
-        <v>256.5</v>
+        <v>7626</v>
       </c>
       <c r="F75" s="1">
-        <v>4495162.5</v>
+        <v>133645650</v>
       </c>
       <c r="G75">
         <f t="shared" si="2"/>
-        <v>348.5</v>
+        <v>7936</v>
       </c>
       <c r="H75">
         <f t="shared" si="3"/>
-        <v>6870602.5</v>
+        <v>141649850</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C76" s="1">
-        <v>310</v>
+        <v>659.8</v>
       </c>
       <c r="D76" s="1">
-        <v>8004200</v>
+        <v>13199998.390000001</v>
       </c>
       <c r="E76" s="1">
-        <v>7626</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1">
-        <v>133645650</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <f t="shared" si="2"/>
-        <v>7936</v>
+        <v>659.8</v>
       </c>
       <c r="H76">
         <f t="shared" si="3"/>
-        <v>141649850</v>
+        <v>13199998.390000001</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="C77" s="1">
-        <v>659.8</v>
+        <v>0</v>
       </c>
       <c r="D77" s="1">
-        <v>13199998.390000001</v>
+        <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="F77" s="1">
-        <v>0</v>
+        <v>7260000</v>
       </c>
       <c r="G77">
         <f t="shared" si="2"/>
-        <v>659.8</v>
+        <v>121</v>
       </c>
       <c r="H77">
         <f t="shared" si="3"/>
-        <v>13199998.390000001</v>
+        <v>7260000</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B78" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C78" s="1">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D78" s="1">
-        <v>0</v>
+        <v>2540000</v>
       </c>
       <c r="E78" s="1">
-        <v>121</v>
+        <v>1233</v>
       </c>
       <c r="F78" s="1">
-        <v>7260000</v>
+        <v>6165000</v>
       </c>
       <c r="G78">
         <f t="shared" si="2"/>
-        <v>121</v>
+        <v>1487</v>
       </c>
       <c r="H78">
         <f t="shared" si="3"/>
-        <v>7260000</v>
+        <v>8705000</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B79" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C79" s="1">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="D79" s="1">
-        <v>2540000</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>1233</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1">
-        <v>6165000</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <f t="shared" si="2"/>
-        <v>1487</v>
+        <v>0</v>
       </c>
       <c r="H79">
         <f t="shared" si="3"/>
-        <v>8705000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B80" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C80" s="1">
         <v>0</v>
@@ -8695,10 +8587,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C81" s="1">
         <v>0</v>
@@ -8707,26 +8599,26 @@
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>2506000</v>
       </c>
       <c r="G81">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="H81">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2506000</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B82" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C82" s="1">
         <v>0</v>
@@ -8735,26 +8627,26 @@
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>2506000</v>
+        <v>0</v>
       </c>
       <c r="G82">
         <f t="shared" si="2"/>
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <f t="shared" si="3"/>
-        <v>2506000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="C83" s="1">
         <v>0</v>
@@ -8763,82 +8655,82 @@
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>15465856</v>
       </c>
       <c r="G83">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H83">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15465856</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C84" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>2100000</v>
       </c>
       <c r="E84" s="1">
-        <v>224</v>
+        <v>104</v>
       </c>
       <c r="F84" s="1">
-        <v>15465856</v>
+        <v>5200000</v>
       </c>
       <c r="G84">
         <f t="shared" si="2"/>
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="H84">
         <f t="shared" si="3"/>
-        <v>15465856</v>
+        <v>7300000</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B85" t="s">
         <v>108</v>
       </c>
       <c r="C85" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D85" s="1">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1">
-        <v>5200000</v>
+        <v>108300</v>
       </c>
       <c r="G85">
         <f t="shared" si="2"/>
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="H85">
         <f t="shared" si="3"/>
-        <v>7300000</v>
+        <v>108300</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="C86" s="1">
         <v>0</v>
@@ -8847,26 +8739,26 @@
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>10</v>
+        <v>187</v>
       </c>
       <c r="F86" s="1">
-        <v>108300</v>
+        <v>2025210</v>
       </c>
       <c r="G86">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>187</v>
       </c>
       <c r="H86">
         <f t="shared" si="3"/>
-        <v>108300</v>
+        <v>2025210</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="C87" s="1">
         <v>0</v>
@@ -8875,23 +8767,23 @@
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="F87" s="1">
-        <v>2025210</v>
+        <v>1300050</v>
       </c>
       <c r="G87">
         <f t="shared" si="2"/>
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="H87">
         <f t="shared" si="3"/>
-        <v>2025210</v>
+        <v>1300050</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
@@ -8903,26 +8795,26 @@
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F88" s="1">
-        <v>1300050</v>
+        <v>0</v>
       </c>
       <c r="G88">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <f t="shared" si="3"/>
-        <v>1300050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C89" s="1">
         <v>0</v>
@@ -8947,10 +8839,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C90" s="1">
         <v>0</v>
@@ -8975,10 +8867,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" s="1">
         <v>0</v>
@@ -9003,7 +8895,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B92" t="s">
         <v>113</v>
@@ -9015,26 +8907,26 @@
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>30000000</v>
       </c>
       <c r="G92">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H92">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30000000</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C93" s="1">
         <v>0</v>
@@ -9043,26 +8935,26 @@
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>3000</v>
+        <v>22</v>
       </c>
       <c r="F93" s="1">
-        <v>30000000</v>
+        <v>220000</v>
       </c>
       <c r="G93">
         <f t="shared" si="2"/>
-        <v>3000</v>
+        <v>22</v>
       </c>
       <c r="H93">
         <f t="shared" si="3"/>
-        <v>30000000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="C94" s="1">
         <v>0</v>
@@ -9071,26 +8963,26 @@
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F94" s="1">
-        <v>220000</v>
+        <v>0</v>
       </c>
       <c r="G94">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <f t="shared" si="3"/>
-        <v>220000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C95" s="1">
         <v>0</v>
@@ -9099,26 +8991,26 @@
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="G95">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H95">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C96" s="1">
         <v>0</v>
@@ -9127,26 +9019,26 @@
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>85</v>
+        <v>1640</v>
       </c>
       <c r="F96" s="1">
-        <v>850000</v>
+        <v>16400000</v>
       </c>
       <c r="G96">
         <f t="shared" si="2"/>
-        <v>85</v>
+        <v>1640</v>
       </c>
       <c r="H96">
         <f t="shared" si="3"/>
-        <v>850000</v>
+        <v>16400000</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="B97" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C97" s="1">
         <v>0</v>
@@ -9155,26 +9047,26 @@
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>1640</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>16400000</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <f t="shared" si="2"/>
-        <v>1640</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <f t="shared" si="3"/>
-        <v>16400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B98" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="C98" s="1">
         <v>0</v>
@@ -9199,10 +9091,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B99" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C99" s="1">
         <v>0</v>
@@ -9227,16 +9119,16 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>151</v>
+        <v>9</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100" s="1">
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>150799946</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
@@ -9246,47 +9138,47 @@
       </c>
       <c r="G100">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>914</v>
       </c>
       <c r="H100">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>150799946</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C101" s="1">
-        <v>914</v>
+        <v>0</v>
       </c>
       <c r="D101" s="1">
-        <v>150799946</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="F101" s="1">
-        <v>0</v>
+        <v>9575280</v>
       </c>
       <c r="G101">
         <f t="shared" si="2"/>
-        <v>914</v>
+        <v>1040</v>
       </c>
       <c r="H101">
         <f t="shared" si="3"/>
-        <v>150799946</v>
+        <v>9575280</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C102" s="1">
         <v>0</v>
@@ -9295,82 +9187,82 @@
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>1040</v>
+        <v>1400</v>
       </c>
       <c r="F102" s="1">
-        <v>9575280</v>
+        <v>1072260</v>
       </c>
       <c r="G102">
         <f t="shared" si="2"/>
-        <v>1040</v>
+        <v>1400</v>
       </c>
       <c r="H102">
         <f t="shared" si="3"/>
-        <v>9575280</v>
+        <v>1072260</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="C103" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103" s="1">
-        <v>0</v>
+        <v>152000</v>
       </c>
       <c r="E103" s="1">
-        <v>1400</v>
+        <v>617</v>
       </c>
       <c r="F103" s="1">
-        <v>1072260</v>
+        <v>8037659</v>
       </c>
       <c r="G103">
         <f t="shared" si="2"/>
-        <v>1400</v>
+        <v>618</v>
       </c>
       <c r="H103">
         <f t="shared" si="3"/>
-        <v>1072260</v>
+        <v>8189659</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
       <c r="C104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="1">
-        <v>152000</v>
+        <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>617</v>
+        <v>769</v>
       </c>
       <c r="F104" s="1">
-        <v>8037659</v>
+        <v>6705680</v>
       </c>
       <c r="G104">
         <f t="shared" si="2"/>
-        <v>618</v>
+        <v>769</v>
       </c>
       <c r="H104">
         <f t="shared" si="3"/>
-        <v>8189659</v>
+        <v>6705680</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B105" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C105" s="1">
         <v>0</v>
@@ -9379,26 +9271,26 @@
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>769</v>
+        <v>28</v>
       </c>
       <c r="F105" s="1">
-        <v>6705680</v>
+        <v>569828</v>
       </c>
       <c r="G105">
         <f t="shared" si="2"/>
-        <v>769</v>
+        <v>28</v>
       </c>
       <c r="H105">
         <f t="shared" si="3"/>
-        <v>6705680</v>
+        <v>569828</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B106" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C106" s="1">
         <v>0</v>
@@ -9407,26 +9299,26 @@
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F106" s="1">
-        <v>569828</v>
+        <v>814040</v>
       </c>
       <c r="G106">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H106">
         <f t="shared" si="3"/>
-        <v>569828</v>
+        <v>814040</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C107" s="1">
         <v>0</v>
@@ -9435,26 +9327,26 @@
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F107" s="1">
-        <v>814040</v>
+        <v>712285</v>
       </c>
       <c r="G107">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H107">
         <f t="shared" si="3"/>
-        <v>814040</v>
+        <v>712285</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C108" s="1">
         <v>0</v>
@@ -9463,26 +9355,26 @@
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F108" s="1">
-        <v>712285</v>
+        <v>956497</v>
       </c>
       <c r="G108">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H108">
         <f t="shared" si="3"/>
-        <v>712285</v>
+        <v>956497</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C109" s="1">
         <v>0</v>
@@ -9491,26 +9383,26 @@
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>47</v>
+        <v>420</v>
       </c>
       <c r="F109" s="1">
-        <v>956497</v>
+        <v>8547420</v>
       </c>
       <c r="G109">
         <f t="shared" si="2"/>
-        <v>47</v>
+        <v>420</v>
       </c>
       <c r="H109">
         <f t="shared" si="3"/>
-        <v>956497</v>
+        <v>8547420</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C110" s="1">
         <v>0</v>
@@ -9519,26 +9411,26 @@
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="F110" s="1">
-        <v>8547420</v>
+        <v>5494770</v>
       </c>
       <c r="G110">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>270</v>
       </c>
       <c r="H110">
         <f t="shared" si="3"/>
-        <v>8547420</v>
+        <v>5494770</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="C111" s="1">
         <v>0</v>
@@ -9547,26 +9439,26 @@
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="F111" s="1">
-        <v>5494770</v>
+        <v>1831590</v>
       </c>
       <c r="G111">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="H111">
         <f t="shared" si="3"/>
-        <v>5494770</v>
+        <v>1831590</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="C112" s="1">
         <v>0</v>
@@ -9575,82 +9467,82 @@
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="F112" s="1">
-        <v>1831590</v>
+        <v>6105300</v>
       </c>
       <c r="G112">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="H112">
         <f t="shared" si="3"/>
-        <v>1831590</v>
+        <v>6105300</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C113" s="1">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="D113" s="1">
-        <v>0</v>
+        <v>1380000</v>
       </c>
       <c r="E113" s="1">
-        <v>300</v>
+        <v>3985.3</v>
       </c>
       <c r="F113" s="1">
-        <v>6105300</v>
+        <v>45021934.100000001</v>
       </c>
       <c r="G113">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>4537.3</v>
       </c>
       <c r="H113">
         <f t="shared" si="3"/>
-        <v>6105300</v>
+        <v>46401934.100000001</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="C114" s="1">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="D114" s="1">
-        <v>1380000</v>
+        <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>3985.3</v>
+        <v>0</v>
       </c>
       <c r="F114" s="1">
-        <v>45021934.100000001</v>
+        <v>0</v>
       </c>
       <c r="G114">
         <f t="shared" si="2"/>
-        <v>4537.3</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <f t="shared" si="3"/>
-        <v>46401934.100000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="C115" s="1">
         <v>0</v>
@@ -9675,10 +9567,10 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C116" s="1">
         <v>0</v>
@@ -9703,10 +9595,10 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
@@ -9731,10 +9623,10 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C118" s="1">
         <v>0</v>
@@ -9759,10 +9651,10 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C119" s="1">
         <v>0</v>
@@ -9787,122 +9679,122 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C120" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D120" s="1">
-        <v>0</v>
+        <v>5760000</v>
       </c>
       <c r="E120" s="1">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="F120" s="1">
-        <v>0</v>
+        <v>89280000</v>
       </c>
       <c r="G120">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1164</v>
       </c>
       <c r="H120">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>95040000</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B121" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="C121" s="1">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D121" s="1">
-        <v>5760000</v>
+        <v>9000000</v>
       </c>
       <c r="E121" s="1">
-        <v>1116</v>
+        <v>268</v>
       </c>
       <c r="F121" s="1">
-        <v>89280000</v>
+        <v>21440000</v>
       </c>
       <c r="G121">
         <f t="shared" si="2"/>
-        <v>1164</v>
+        <v>343</v>
       </c>
       <c r="H121">
         <f t="shared" si="3"/>
-        <v>95040000</v>
+        <v>30440000</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B122" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="C122" s="1">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="D122" s="1">
-        <v>9000000</v>
+        <v>55440000</v>
       </c>
       <c r="E122" s="1">
-        <v>268</v>
+        <v>444</v>
       </c>
       <c r="F122" s="1">
-        <v>21440000</v>
+        <v>62160000</v>
       </c>
       <c r="G122">
         <f t="shared" si="2"/>
-        <v>343</v>
+        <v>708</v>
       </c>
       <c r="H122">
         <f t="shared" si="3"/>
-        <v>30440000</v>
+        <v>117600000</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B123" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C123" s="1">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="D123" s="1">
-        <v>55440000</v>
+        <v>2400000</v>
       </c>
       <c r="E123" s="1">
-        <v>444</v>
+        <v>60</v>
       </c>
       <c r="F123" s="1">
-        <v>62160000</v>
+        <v>4800000</v>
       </c>
       <c r="G123">
         <f t="shared" si="2"/>
-        <v>708</v>
+        <v>80</v>
       </c>
       <c r="H123">
         <f t="shared" si="3"/>
-        <v>117600000</v>
+        <v>7200000</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B124" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C124" s="1">
         <v>20</v>
@@ -9911,116 +9803,116 @@
         <v>2400000</v>
       </c>
       <c r="E124" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F124" s="1">
-        <v>4800000</v>
+        <v>4000000</v>
       </c>
       <c r="G124">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H124">
         <f t="shared" si="3"/>
-        <v>7200000</v>
+        <v>6400000</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B125" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C125" s="1">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D125" s="1">
-        <v>2400000</v>
+        <v>7560000</v>
       </c>
       <c r="E125" s="1">
-        <v>50</v>
+        <v>858</v>
       </c>
       <c r="F125" s="1">
-        <v>4000000</v>
+        <v>68640000</v>
       </c>
       <c r="G125">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>921</v>
       </c>
       <c r="H125">
         <f t="shared" si="3"/>
-        <v>6400000</v>
+        <v>76200000</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="C126" s="1">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D126" s="1">
-        <v>7560000</v>
+        <v>900000</v>
       </c>
       <c r="E126" s="1">
-        <v>858</v>
+        <v>31</v>
       </c>
       <c r="F126" s="1">
-        <v>68640000</v>
+        <v>248000</v>
       </c>
       <c r="G126">
         <f t="shared" si="2"/>
-        <v>921</v>
+        <v>131</v>
       </c>
       <c r="H126">
         <f t="shared" si="3"/>
-        <v>76200000</v>
+        <v>1148000</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C127" s="1">
-        <v>100</v>
+        <v>720</v>
       </c>
       <c r="D127" s="1">
-        <v>900000</v>
+        <v>36000000</v>
       </c>
       <c r="E127" s="1">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F127" s="1">
-        <v>248000</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <f t="shared" si="2"/>
-        <v>131</v>
+        <v>720</v>
       </c>
       <c r="H127">
         <f t="shared" si="3"/>
-        <v>1148000</v>
+        <v>36000000</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C128" s="1">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="D128" s="1">
-        <v>36000000</v>
+        <v>0</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
@@ -10030,131 +9922,131 @@
       </c>
       <c r="G128">
         <f t="shared" si="2"/>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="H128">
         <f t="shared" si="3"/>
-        <v>36000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B129" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C129" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D129" s="1">
-        <v>0</v>
+        <v>1352000</v>
       </c>
       <c r="E129" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1">
-        <v>0</v>
+        <v>260000</v>
       </c>
       <c r="G129">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H129">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1612000</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C130" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D130" s="1">
-        <v>1352000</v>
+        <v>1600000</v>
       </c>
       <c r="E130" s="1">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="F130" s="1">
-        <v>260000</v>
+        <v>4240000</v>
       </c>
       <c r="G130">
         <f t="shared" si="2"/>
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="H130">
         <f t="shared" si="3"/>
-        <v>1612000</v>
+        <v>5840000</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B131" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="C131" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D131" s="1">
-        <v>1600000</v>
+        <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>212</v>
+        <v>40</v>
       </c>
       <c r="F131" s="1">
-        <v>4240000</v>
+        <v>988000</v>
       </c>
       <c r="G131">
-        <f t="shared" si="2"/>
-        <v>220</v>
+        <f t="shared" ref="G131:G159" si="4">C131+E131</f>
+        <v>40</v>
       </c>
       <c r="H131">
-        <f t="shared" si="3"/>
-        <v>5840000</v>
+        <f t="shared" ref="H131:H159" si="5">D131+F131</f>
+        <v>988000</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B132" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="C132" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D132" s="1">
-        <v>0</v>
+        <v>1700000</v>
       </c>
       <c r="E132" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F132" s="1">
-        <v>0</v>
+        <v>1700000</v>
       </c>
       <c r="G132">
-        <f t="shared" ref="G132:G162" si="4">C132+E132</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>15</v>
       </c>
       <c r="H132">
-        <f t="shared" ref="H132:H162" si="5">D132+F132</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>3400000</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="B133" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="C133" s="1">
         <v>0</v>
@@ -10163,82 +10055,82 @@
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F133" s="1">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="G133">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H133">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B134" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C134" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D134" s="1">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="E134" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F134" s="1">
-        <v>988000</v>
+        <v>350000</v>
       </c>
       <c r="G134">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>10.8</v>
       </c>
       <c r="H134">
         <f t="shared" si="5"/>
-        <v>988000</v>
+        <v>390000</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C135" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D135" s="1">
-        <v>1700000</v>
+        <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F135" s="1">
-        <v>1700000</v>
+        <v>0</v>
       </c>
       <c r="G135">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H135">
         <f t="shared" si="5"/>
-        <v>3400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B136" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C136" s="1">
         <v>0</v>
@@ -10247,60 +10139,60 @@
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F136" s="1">
-        <v>1050000</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H136">
         <f t="shared" si="5"/>
-        <v>1050000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>83</v>
       </c>
       <c r="C137" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D137" s="1">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>10</v>
+        <v>26.3</v>
       </c>
       <c r="F137" s="1">
-        <v>350000</v>
+        <v>295007.09999999998</v>
       </c>
       <c r="G137">
         <f t="shared" si="4"/>
-        <v>10.8</v>
+        <v>26.3</v>
       </c>
       <c r="H137">
         <f t="shared" si="5"/>
-        <v>390000</v>
+        <v>295007.09999999998</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C138" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D138" s="1">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
@@ -10310,19 +10202,19 @@
       </c>
       <c r="G138">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H138">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C139" s="1">
         <v>0</v>
@@ -10331,26 +10223,26 @@
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="F139" s="1">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="G139">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H139">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B140" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="C140" s="1">
         <v>0</v>
@@ -10359,54 +10251,54 @@
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="F140" s="1">
-        <v>295007.09999999998</v>
+        <v>0</v>
       </c>
       <c r="G140">
         <f t="shared" si="4"/>
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="H140">
         <f t="shared" si="5"/>
-        <v>295007.09999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C141" s="1">
         <v>2</v>
       </c>
       <c r="D141" s="1">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="E141" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F141" s="1">
-        <v>0</v>
+        <v>480000</v>
       </c>
       <c r="G141">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="H141">
         <f t="shared" si="5"/>
-        <v>600000</v>
+        <v>680000</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C142" s="1">
         <v>0</v>
@@ -10415,26 +10307,26 @@
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>1.75</v>
+        <v>1500</v>
       </c>
       <c r="F142" s="1">
-        <v>350000</v>
+        <v>45000000</v>
       </c>
       <c r="G142">
         <f t="shared" si="4"/>
-        <v>1.75</v>
+        <v>1500</v>
       </c>
       <c r="H142">
         <f t="shared" si="5"/>
-        <v>350000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B143" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C143" s="1">
         <v>0</v>
@@ -10443,82 +10335,82 @@
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F143" s="1">
-        <v>0</v>
+        <v>1050000</v>
       </c>
       <c r="G143">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H143">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B144" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
       <c r="C144" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D144" s="1">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F144" s="1">
-        <v>480000</v>
+        <v>749999.88</v>
       </c>
       <c r="G144">
         <f t="shared" si="4"/>
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H144">
         <f t="shared" si="5"/>
-        <v>680000</v>
+        <v>749999.88</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B145" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C145" s="1">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D145" s="1">
-        <v>0</v>
+        <v>6750018.54</v>
       </c>
       <c r="E145" s="1">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F145" s="1">
-        <v>45000000</v>
+        <v>0</v>
       </c>
       <c r="G145">
         <f t="shared" si="4"/>
-        <v>1500</v>
+        <v>58</v>
       </c>
       <c r="H145">
         <f t="shared" si="5"/>
-        <v>45000000</v>
+        <v>6750018.54</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C146" s="1">
         <v>0</v>
@@ -10527,26 +10419,26 @@
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1">
-        <v>1050000</v>
+        <v>1260000</v>
       </c>
       <c r="G146">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="H146">
         <f t="shared" si="5"/>
-        <v>1050000</v>
+        <v>1260000</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
-        <v>176</v>
+        <v>81</v>
       </c>
       <c r="C147" s="1">
         <v>0</v>
@@ -10555,54 +10447,54 @@
         <v>0</v>
       </c>
       <c r="E147" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F147" s="1">
-        <v>749999.88</v>
+        <v>0</v>
       </c>
       <c r="G147">
         <f t="shared" si="4"/>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <f t="shared" si="5"/>
-        <v>749999.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C148" s="1">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D148" s="1">
-        <v>6750018.54</v>
+        <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="F148" s="1">
-        <v>0</v>
+        <v>2832000</v>
       </c>
       <c r="G148">
         <f t="shared" si="4"/>
-        <v>58</v>
+        <v>236</v>
       </c>
       <c r="H148">
         <f t="shared" si="5"/>
-        <v>6750018.54</v>
+        <v>2832000</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="C149" s="1">
         <v>0</v>
@@ -10611,26 +10503,26 @@
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="F149" s="1">
-        <v>1260000</v>
+        <v>2604000</v>
       </c>
       <c r="G149">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="H149">
         <f t="shared" si="5"/>
-        <v>1260000</v>
+        <v>2604000</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B150" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C150" s="1">
         <v>0</v>
@@ -10639,26 +10531,26 @@
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G150">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H150">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B151" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C151" s="1">
         <v>0</v>
@@ -10667,26 +10559,26 @@
         <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>236</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1">
-        <v>2832000</v>
+        <v>46668</v>
       </c>
       <c r="G151">
         <f t="shared" si="4"/>
-        <v>236</v>
+        <v>4</v>
       </c>
       <c r="H151">
         <f t="shared" si="5"/>
-        <v>2832000</v>
+        <v>46668</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B152" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="C152" s="1">
         <v>0</v>
@@ -10695,26 +10587,26 @@
         <v>0</v>
       </c>
       <c r="E152" s="1">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1">
-        <v>2604000</v>
+        <v>780000</v>
       </c>
       <c r="G152">
         <f t="shared" si="4"/>
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="H152">
         <f t="shared" si="5"/>
-        <v>2604000</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B153" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C153" s="1">
         <v>0</v>
@@ -10723,26 +10615,26 @@
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1">
-        <v>100000</v>
+        <v>6000000</v>
       </c>
       <c r="G153">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H153">
         <f t="shared" si="5"/>
-        <v>100000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B154" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C154" s="1">
         <v>0</v>
@@ -10751,26 +10643,26 @@
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F154" s="1">
-        <v>46668</v>
+        <v>822640</v>
       </c>
       <c r="G154">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H154">
         <f t="shared" si="5"/>
-        <v>46668</v>
+        <v>822640</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B155" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C155" s="1">
         <v>0</v>
@@ -10779,26 +10671,26 @@
         <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1">
-        <v>780000</v>
+        <v>1500000</v>
       </c>
       <c r="G155">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H155">
         <f t="shared" si="5"/>
-        <v>780000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="C156" s="1">
         <v>0</v>
@@ -10807,54 +10699,54 @@
         <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F156" s="1">
-        <v>6000000</v>
+        <v>1400000</v>
       </c>
       <c r="G156">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H156">
         <f t="shared" si="5"/>
-        <v>6000000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B157" t="s">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="C157" s="1">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="D157" s="1">
-        <v>0</v>
+        <v>33419.879999999997</v>
       </c>
       <c r="E157" s="1">
-        <v>14</v>
+        <v>30.83</v>
       </c>
       <c r="F157" s="1">
-        <v>822640</v>
+        <v>801580</v>
       </c>
       <c r="G157">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>31.2</v>
       </c>
       <c r="H157">
         <f t="shared" si="5"/>
-        <v>822640</v>
+        <v>834999.88</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B158" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C158" s="1">
         <v>0</v>
@@ -10863,113 +10755,29 @@
         <v>0</v>
       </c>
       <c r="E158" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F158" s="1">
-        <v>1500000</v>
+        <v>100000</v>
       </c>
       <c r="G158">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H158">
         <f t="shared" si="5"/>
-        <v>1500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>145</v>
-      </c>
-      <c r="B159" t="s">
-        <v>171</v>
-      </c>
-      <c r="C159" s="1">
-        <v>0</v>
-      </c>
-      <c r="D159" s="1">
-        <v>0</v>
-      </c>
-      <c r="E159" s="1">
-        <v>14</v>
-      </c>
-      <c r="F159" s="1">
-        <v>1400000</v>
+      <c r="D159">
+        <v>0</v>
       </c>
       <c r="G159">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <f t="shared" si="5"/>
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>145</v>
-      </c>
-      <c r="B160" t="s">
-        <v>170</v>
-      </c>
-      <c r="C160" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="D160" s="1">
-        <v>33419.879999999997</v>
-      </c>
-      <c r="E160" s="1">
-        <v>30.83</v>
-      </c>
-      <c r="F160" s="1">
-        <v>801580</v>
-      </c>
-      <c r="G160">
-        <f t="shared" si="4"/>
-        <v>31.2</v>
-      </c>
-      <c r="H160">
-        <f t="shared" si="5"/>
-        <v>834999.88</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>145</v>
-      </c>
-      <c r="B161" t="s">
-        <v>48</v>
-      </c>
-      <c r="C161" s="1">
-        <v>0</v>
-      </c>
-      <c r="D161" s="1">
-        <v>0</v>
-      </c>
-      <c r="E161" s="1">
-        <v>5</v>
-      </c>
-      <c r="F161" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G161">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H161">
-        <f t="shared" si="5"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="G162">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H162">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
